--- a/public/files/_quotations/ใบเสนอราคา_Smart Thatoom Super App.xlsx
+++ b/public/files/_quotations/ใบเสนอราคา_Smart Thatoom Super App.xlsx
@@ -1,20 +1,20 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
-  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
-  <AppVersion>3.1</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super App" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
-  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
-  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-11T17:32:17Z</dcterms:created>
-  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-11T17:32:17Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="10">
@@ -244,7 +244,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -527,22 +527,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super App" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
